--- a/ESE/Attendance ESE 2-1.xlsx
+++ b/ESE/Attendance ESE 2-1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Attendance\ESE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8936BD6A-7645-4957-A022-EE6E9FF99113}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E35F02E-B86A-4D41-B57F-3F10EE7E96A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
